--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T12:22:36+00:00</t>
+    <t>2026-09-17T12:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:59:08+00:00</t>
+    <t>2026-09-28T13:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:01:57+00:00</t>
+    <t>2026-09-28T14:15:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:15:25+00:00</t>
+    <t>2026-09-28T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:29:01+00:00</t>
+    <t>2026-09-28T14:57:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:57:10+00:00</t>
+    <t>2026-09-29T08:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:00:45+00:00</t>
+    <t>2026-09-29T11:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:55:38+00:00</t>
+    <t>2026-10-08T14:23:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>81</v>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>81</v>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:30:19+00:00</t>
+    <t>2026-10-13T07:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
